--- a/04-实施战略/03-实施工具/03-价值流图模板.xlsx
+++ b/04-实施战略/03-实施工具/03-价值流图模板.xlsx
@@ -99,7 +99,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -126,11 +126,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +161,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -535,7 +545,13 @@
           <t>03-价值流图模板</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -543,6 +559,10 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -550,6 +570,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -557,6 +578,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
@@ -595,7 +617,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  │ 冷镦  │──→│ 搓丝  │──→│ 热处理 │──→│ 表面  │──→│ 包装  │──→ 客户</t>
+          <t xml:space="preserve">  │ 机加工  │──→│ 精加工  │──→│ 热处理 │──→│ 表面  │──→│ 包装  │──→ 客户</t>
         </is>
       </c>
     </row>
@@ -620,6 +642,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
@@ -627,6 +650,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
@@ -634,6 +658,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
@@ -641,6 +666,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
@@ -662,6 +688,9 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -669,6 +698,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
@@ -676,6 +706,9 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -683,6 +716,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
@@ -690,6 +724,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
@@ -746,6 +781,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
@@ -753,6 +789,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
@@ -802,6 +839,9 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
@@ -809,6 +849,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
